--- a/artfynd/A 49764-2025 artfynd.xlsx
+++ b/artfynd/A 49764-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115107971</v>
+        <v>115107726</v>
       </c>
       <c r="B2" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>869166</v>
+        <v>868936</v>
       </c>
       <c r="R2" t="n">
-        <v>7443889</v>
+        <v>7443759</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115107929</v>
+        <v>115107971</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>869108</v>
+        <v>869166</v>
       </c>
       <c r="R3" t="n">
-        <v>7443839</v>
+        <v>7443889</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -887,19 +877,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115107917</v>
+        <v>115107797</v>
       </c>
       <c r="B4" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -930,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>869100</v>
+        <v>869035</v>
       </c>
       <c r="R4" t="n">
-        <v>7443851</v>
+        <v>7443852</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -993,51 +978,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115108039</v>
+        <v>115107895</v>
       </c>
       <c r="B5" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,13 +1016,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>869362</v>
+        <v>869019</v>
       </c>
       <c r="R5" t="n">
-        <v>7444035</v>
+        <v>7443867</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,6 +1060,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1107,19 +1079,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115107948</v>
+        <v>115107909</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1150,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>869149</v>
+        <v>869021</v>
       </c>
       <c r="R6" t="n">
-        <v>7443902</v>
+        <v>7443870</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1213,19 +1180,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115107895</v>
+        <v>115107917</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1256,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>869019</v>
+        <v>869100</v>
       </c>
       <c r="R7" t="n">
-        <v>7443867</v>
+        <v>7443851</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1319,43 +1281,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115108069</v>
+        <v>115107929</v>
       </c>
       <c r="B8" t="n">
-        <v>55873</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1363,13 +1319,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>869292</v>
+        <v>869108</v>
       </c>
       <c r="R8" t="n">
-        <v>7443945</v>
+        <v>7443839</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,6 +1363,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1425,19 +1382,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115107909</v>
+        <v>115107948</v>
       </c>
       <c r="B9" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1468,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>869021</v>
+        <v>869149</v>
       </c>
       <c r="R9" t="n">
-        <v>7443870</v>
+        <v>7443902</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1531,43 +1483,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115108086</v>
+        <v>115107992</v>
       </c>
       <c r="B10" t="n">
-        <v>56470</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1575,13 +1521,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>869292</v>
+        <v>869378</v>
       </c>
       <c r="R10" t="n">
-        <v>7443945</v>
+        <v>7444047</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1619,6 +1565,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1637,56 +1584,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115107992</v>
+        <v>115108291</v>
       </c>
       <c r="B11" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kulmunkivuoma, Nb</t>
+          <t>Kulmunkivuoma, Aapua, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>869378</v>
+        <v>869222</v>
       </c>
       <c r="R11" t="n">
-        <v>7444047</v>
+        <v>7443939</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1724,7 +1667,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1746,16 +1688,11 @@
         <v>115108149</v>
       </c>
       <c r="B12" t="n">
-        <v>56115</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56766</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1849,32 +1786,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115108291</v>
+        <v>115108086</v>
       </c>
       <c r="B13" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1889,17 +1821,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kulmunkivuoma, Aapua, Nb</t>
+          <t>Kulmunkivuoma, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>869222</v>
+        <v>869292</v>
       </c>
       <c r="R13" t="n">
-        <v>7443939</v>
+        <v>7443945</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1955,15 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115107797</v>
+        <v>115108039</v>
       </c>
       <c r="B14" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,26 +1898,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1998,13 +1934,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>869035</v>
+        <v>869362</v>
       </c>
       <c r="R14" t="n">
-        <v>7443852</v>
+        <v>7444035</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2042,7 +1978,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2058,6 +1993,107 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>115108069</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kulmunkivuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>869292</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7443945</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49764-2025 artfynd.xlsx
+++ b/artfynd/A 49764-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115107726</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115107971</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115107797</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115107895</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115107909</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115107917</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115107929</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115107948</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115107992</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115108291</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115108149</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115108086</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1993,6 +2058,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115108039</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2094,8 +2164,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115108069</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>